--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2024/American_Aircraft_Cumulative_Statistics_2024.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2024/American_Aircraft_Cumulative_Statistics_2024.xlsx
@@ -221,13 +221,13 @@
         <v>670</v>
       </c>
       <c r="K2" s="0">
-        <v>4488</v>
+        <v>4487.8100000000004</v>
       </c>
       <c r="L2" s="0">
         <v>35.060000000000002</v>
       </c>
       <c r="M2" s="0">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="3">
@@ -262,13 +262,13 @@
         <v>687</v>
       </c>
       <c r="K3" s="0">
-        <v>5077</v>
+        <v>5077.1700000000001</v>
       </c>
       <c r="L3" s="0">
         <v>33.850000000000001</v>
       </c>
       <c r="M3" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10199999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -303,13 +303,13 @@
         <v>1074</v>
       </c>
       <c r="K4" s="0">
-        <v>6518</v>
+        <v>6518.3299999999999</v>
       </c>
       <c r="L4" s="0">
         <v>35.729999999999997</v>
       </c>
       <c r="M4" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
     <row r="5">
@@ -344,13 +344,13 @@
         <v>1742</v>
       </c>
       <c r="K5" s="0">
-        <v>7113</v>
+        <v>7113.1599999999999</v>
       </c>
       <c r="L5" s="0">
         <v>36.380000000000003</v>
       </c>
       <c r="M5" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="6">
@@ -385,13 +385,13 @@
         <v>916</v>
       </c>
       <c r="K6" s="0">
-        <v>5773</v>
+        <v>5772.7200000000003</v>
       </c>
       <c r="L6" s="0">
         <v>33.560000000000002</v>
       </c>
       <c r="M6" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -426,13 +426,13 @@
         <v>1237</v>
       </c>
       <c r="K7" s="0">
-        <v>5836</v>
+        <v>5835.8699999999999</v>
       </c>
       <c r="L7" s="0">
         <v>33.93</v>
       </c>
       <c r="M7" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="8">
@@ -467,13 +467,13 @@
         <v>4106</v>
       </c>
       <c r="K8" s="0">
-        <v>11111</v>
+        <v>11110.67</v>
       </c>
       <c r="L8" s="0">
         <v>47.530000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
     <row r="9">
@@ -508,13 +508,13 @@
         <v>4442</v>
       </c>
       <c r="K9" s="0">
-        <v>13103</v>
+        <v>13102.6</v>
       </c>
       <c r="L9" s="0">
         <v>46.039999999999999</v>
       </c>
       <c r="M9" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -549,13 +549,13 @@
         <v>3987</v>
       </c>
       <c r="K10" s="0">
-        <v>13642</v>
+        <v>13642.299999999999</v>
       </c>
       <c r="L10" s="0">
         <v>50.159999999999997</v>
       </c>
       <c r="M10" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10299999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -590,13 +590,13 @@
         <v>4606</v>
       </c>
       <c r="K11" s="0">
-        <v>15583</v>
+        <v>15583.18</v>
       </c>
       <c r="L11" s="0">
         <v>51.259999999999998</v>
       </c>
       <c r="M11" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="12">
@@ -631,13 +631,13 @@
         <v>1154</v>
       </c>
       <c r="K12" s="0">
-        <v>7024</v>
+        <v>7023.9799999999996</v>
       </c>
       <c r="L12" s="0">
         <v>37.869999999999997</v>
       </c>
       <c r="M12" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
   </sheetData>
